--- a/db/cellxgene/our_markers.xlsx
+++ b/db/cellxgene/our_markers.xlsx
@@ -847,7 +847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X43"/>
+  <dimension ref="A1:X54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5448,6 +5448,1161 @@
         </is>
       </c>
       <c r="X43" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>M00043</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>9</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CELLxGENE:3dc61ca1-ce40-46b6-8337-f27260fd9a03</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>DOI_10.1016_j.cell.2022.11.005</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>DOI_10.1016_j.cell.2022.11.005</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>neuroendocrine cell</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>GHRL</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>GHRL</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>figure_labeled</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>formal_candidate</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Figure 2F</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>GHRL+ neuroendocrine cells are shown in red in fetal human lung in situ HCR.</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>GLM预筛后定向复核：作者图注明确标注GHRL+ neuroendocrine；未逐句全文复核</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1016_j.cell.2022.11.005.md</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>M00044</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>9</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CELLxGENE:3dc61ca1-ce40-46b6-8337-f27260fd9a03</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DOI_10.1016_j.cell.2022.11.005</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>DOI_10.1016_j.cell.2022.11.005</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>pulmonary neuroendocrine cell</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>GRP</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>GRP</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>figure_labeled</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>formal_candidate</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Figure 2F</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>GRP+ pulmonary neuroendocrine cells are shown in green in fetal human lung in situ HCR.</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>GLM预筛后定向复核：作者图注明确标注GRP+ pulmonary neuroendocrine</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1016_j.cell.2022.11.005.md</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>M00045</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>9</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CELLxGENE:3dc61ca1-ce40-46b6-8337-f27260fd9a03</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DOI_10.1016_j.cell.2022.11.005</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>DOI_10.1016_j.cell.2022.11.005</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>pulmonary neuroendocrine cell</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>ASCL1</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>ASCL1</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>figure_labeled</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>formal_candidate</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Figure S3K</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>ASCL1+ pulmonary neuroendocrine cells are identified in fetal lung airway regions.</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>GLM预筛后定向复核：作者图注明确标注ASCL1+ pulmonary neuroendocrine</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1016_j.cell.2022.11.005.md</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>M00046</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>9</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CELLxGENE:3dc61ca1-ce40-46b6-8337-f27260fd9a03</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DOI_10.1016_j.cell.2022.11.005</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DOI_10.1016_j.cell.2022.11.005</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>neuroendocrine cell</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>NEUROD1</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>NEUROD1</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>figure_labeled</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>formal_candidate</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Figure 7E</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>HCR and quantification identify NEUROD1+ neuroendocrine cell types in human fetal lungs.</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>GLM预筛后定向复核：保留作者Figure 7中的NEUROD1+细胞标注</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1016_j.cell.2022.11.005.md</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>M00047</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>12</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CELLxGENE:781cc817-3fd0-487c-a55a-b47b2786a05d</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s44318-024-00328-6</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s44318-024-00328-6</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>neuroendocrine cell</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>ASCL1</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>ASCL1</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>figure_labeled</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>formal_candidate</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Figure EV2H</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>UMAP plots show transcript expression of ASCL1 for the neuroendocrine lineage in fdAT2 organoids.</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>GLM预筛后定向复核：Figure EV2直接展示神经内分泌相关转录本</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1038_s44318-024-00328-6.md</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>M00048</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CELLxGENE:781cc817-3fd0-487c-a55a-b47b2786a05d</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s44318-024-00328-6</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s44318-024-00328-6</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>neuroendocrine cell</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>NEUROD1</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>NEUROD1</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>figure_labeled</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>formal_candidate</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Figure EV2I</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>UMAP plots label neuroendocrine cells with NEUROD1 transcript expression.</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>GLM预筛后定向复核：Figure EV2图注明确对应neuroendocrine cells</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1038_s44318-024-00328-6.md</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>M00049</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>12</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CELLxGENE:781cc817-3fd0-487c-a55a-b47b2786a05d</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s44318-024-00328-6</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s44318-024-00328-6</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>neuroendocrine cell</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>GRP</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>GRP</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>figure_labeled</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>formal_candidate</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Figure EV2I</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>UMAP plots label neuroendocrine cells with GRP transcript expression.</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>GLM预筛后定向复核：Figure EV2图注明确对应neuroendocrine cells</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1038_s44318-024-00328-6.md</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>M00050</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>21</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CELLxGENE:fb5eeccf-3c2a-473c-b6e3-7a1dda18d42d</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DOI_10.64898_2025.12.18.695268</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>DOI_10.64898_2025.12.18.695268</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Schwann cell</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>XKR4</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>XKR4</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>author_declared</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>formal_candidate</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Results; Fig. 1C</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Additional stromal populations included Schwann cells (NRXN+/XKR4+).</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>作者正文直接给出Schwann cell阳性标记；不完整符号NRXN未录入</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.64898_2025.12.18.695268.md</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>M00051</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>21</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CELLxGENE:fb5eeccf-3c2a-473c-b6e3-7a1dda18d42d</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DOI_10.64898_2025.12.18.695268</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>DOI_10.64898_2025.12.18.695268</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Schwann cell</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>NRXN1</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>NRXN1</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>author_declared</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>formal_candidate</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Results; Fig. S3E</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Regions surrounding innervating structures featured Schwann cells (NRXN1+).</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>作者正文直接给出Schwann cells (NRXN1+)</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.64898_2025.12.18.695268.md</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>M00052</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>24</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CELLxGENE:8b2e5453-faf7-46ea-9073-aea69b283cb7</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DOI_10.1002_pros.24020</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>DOI_10.1002_pros.24020</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>neuroendocrine cell</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>CALCA</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>CGRP</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>author_declared</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>formal_candidate</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Results §3.1; Figure S3A,C</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Neuroendocrine epithelia can be identified using known markers such as CGRP and CHGA.</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>作者直接称为known markers；CGRP规范化为基因符号CALCA</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1002_pros.24020.md</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>M00053</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>24</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CELLxGENE:8b2e5453-faf7-46ea-9073-aea69b283cb7</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DOI_10.1002_pros.24020</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>DOI_10.1002_pros.24020</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>neuroendocrine cell</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>CHGA</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>CHGA</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>author_declared</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>formal_candidate</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Results §3.1; Figure S3A,C</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Neuroendocrine epithelia can be identified using known markers such as CGRP and CHGA.</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>作者直接称为known markers</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1002_pros.24020.md</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
@@ -5486,7 +6641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7978,6 +9133,1707 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41586-021-03710-0</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41586-021-03710-0</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Dysregulation of brain and choroid plexus cell types in severe COVID-19.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1038_s41586-021-03710-0.md</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>markdown_review_no_formal: Markdown定向复核未发现作者直接给出的正式PNS marker；窗口共现或比较文献基因不录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41586-020-2922-4</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41586-020-2922-4</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>A molecular cell atlas of the human lung from single-cell RNA sequencing.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1038_s41586-020-2922-4.md</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>markdown_review_no_formal: Markdown定向复核未发现作者直接给出的正式PNS marker；窗口共现或比较文献基因不录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>7</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41586-021-04345-x</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41586-021-04345-x</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Local and systemic responses to SARS-CoV-2 infection in children and adults.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1038_s41586-021-04345-x.md</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>needs_manual_review: Markdown提及PNS细胞，但marker疑位于未完整转换的图表或补充材料，暂不强行录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>8</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DOI_10.1016_j.jcf.2025.01.016</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>DOI_10.1016_j.jcf.2025.01.016</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Evidence for altered immune-structural cell crosstalk in cystic fibrosis revealed by single cell transcriptomics.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1016_j.jcf.2025.01.016.md</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>markdown_review_no_formal: Markdown定向复核未发现作者直接给出的正式PNS marker；窗口共现或比较文献基因不录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>9</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DOI_10.1016_j.cell.2022.11.005</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DOI_10.1016_j.cell.2022.11.005</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>A human fetal lung cell atlas uncovers proximal-distal gradients of differentiation and key regulators of epithelial fates.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>4</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1016_j.cell.2022.11.005.md</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>markdown_review_imported: GLM预筛后经Markdown定向复核，批准并录入4条；窗口误配候选已剔除</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>11</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DOI_10.7554_elife.62522</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DOI_10.7554_elife.62522</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Single-cell multiomic profiling of human lungs reveals cell-type-specific and age-dynamic control of SARS-CoV2 host genes.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.7554_elife.62522.md</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>needs_manual_review: Markdown提及PNS细胞，但marker疑位于未完整转换的图表或补充材料，暂不强行录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>12</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s44318-024-00328-6</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s44318-024-00328-6</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>A novel human fetal lung-derived alveolar organoid model reveals mechanisms of surfactant protein C maturation relevant to interstitial lung disease.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1038_s44318-024-00328-6.md</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>markdown_review_imported: GLM预筛后经Markdown定向复核，批准并录入3条；窗口误配候选已剔除</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>13</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DOI_10.1126_sciimmunol.adf9988</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DOI_10.1126_sciimmunol.adf9988</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Early human lung immune cell development and its role in epithelial cell fate.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1126_sciimmunol.adf9988.md</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>markdown_review_no_formal: Markdown定向复核未发现作者直接给出的正式PNS marker；窗口共现或比较文献基因不录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>15</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41467-023-40173-5</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41467-023-40173-5</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Guided construction of single cell reference for human and mouse lung.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1038_s41467-023-40173-5.md</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>needs_manual_review: Markdown提及PNS细胞，但marker疑位于未完整转换的图表或补充材料，暂不强行录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>16</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41588-024-01702-0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41588-024-01702-0</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Cell-type-specific and disease-associated expression quantitative trait loci in the human lung.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1038_s41588-024-01702-0.md</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>markdown_review_no_formal: Markdown定向复核未发现作者直接给出的正式PNS marker；窗口共现或比较文献基因不录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>17</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41586-021-03569-1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41586-021-03569-1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>A molecular single-cell lung atlas of lethal COVID-19.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1038_s41586-021-03569-1.md</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>needs_manual_review: Markdown提及PNS细胞，但marker疑位于未完整转换的图表或补充材料，暂不强行录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>18</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DOI_10.1016_j.stem.2022.11.013</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DOI_10.1016_j.stem.2022.11.013</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Organoid modeling of human fetal lung alveolar development reveals mechanisms of cell fate patterning and neonatal respiratory disease.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1016_j.stem.2022.11.013.md</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>markdown_review_no_formal: Markdown定向复核未发现作者直接给出的正式PNS marker；窗口共现或比较文献基因不录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>20</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DOI_10.1016_j.cell.2021.07.023</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DOI_10.1016_j.cell.2021.07.023</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Impaired local intrinsic immunity to SARS-CoV-2 infection in severe COVID-19.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1016_j.cell.2021.07.023.md</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>needs_manual_review: Markdown提及PNS细胞，但marker疑位于未完整转换的图表或补充材料，暂不强行录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>21</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DOI_10.64898_2025.12.18.695268</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DOI_10.64898_2025.12.18.695268</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>A poly(A) isoform–aware single-cell and spatial atlas defines fibroblast niches in the human bladder</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.64898_2025.12.18.695268.md</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>markdown_review_imported: GLM预筛后经Markdown定向复核，批准并录入2条；窗口误配候选已剔除</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>22</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DOI_10.1126_science.aat5031</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DOI_10.1126_science.aat5031</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Spatiotemporal immune zonation of the human kidney.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1126_science.aat5031.md</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>markdown_review_no_formal: Markdown定向复核未发现作者直接给出的正式PNS marker；窗口共现或比较文献基因不录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>24</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DOI_10.1002_pros.24020</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>DOI_10.1002_pros.24020</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Urethral luminal epithelia are castration-insensitive cells of the proximal prostate.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1002_pros.24020.md</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>markdown_review_imported: GLM预筛后经Markdown定向复核，批准并录入2条；窗口误配候选已剔除</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>28</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DOI_10.1016_j.cell.2017.09.004</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DOI_10.1016_j.cell.2017.09.004</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Single-Cell Analysis of Human Pancreas Reveals Transcriptional Signatures of Aging and Somatic Mutation Patterns.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1016_j.cell.2017.09.004.md</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>markdown_review_no_formal: Markdown定向复核未发现作者直接给出的正式PNS marker；窗口共现或比较文献基因不录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>29</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41591-024-03215-z</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41591-024-03215-z</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>A multi-modal single-cell and spatial expression map of metastatic breast cancer biopsies across clinicopathological features.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1038_s41591-024-03215-z.md</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>markdown_review_no_formal: Markdown定向复核未发现作者直接给出的正式PNS marker；窗口共现或比较文献基因不录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>30</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s42003-021-02562-8</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s42003-021-02562-8</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Identification of distinct tumor cell populations and key genetic mechanisms through single cell sequencing in hepatoblastoma.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1038_s42003-021-02562-8.md</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>markdown_review_no_formal: Markdown定向复核未发现作者直接给出的正式PNS marker；窗口共现或比较文献基因不录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>32</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41586-021-03929-x</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41586-021-03929-x</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Blood and immune development in human fetal bone marrow and Down syndrome.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1038_s41586-021-03929-x.md</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>markdown_review_no_formal: Markdown定向复核未发现作者直接给出的正式PNS marker；窗口共现或比较文献基因不录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>33</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41588-025-02182-6</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41588-025-02182-6</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>An integrated transcriptomic cell atlas of human endoderm-derived organoids.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1038_s41588-025-02182-6.md</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>needs_manual_review: Markdown提及PNS细胞，但marker疑位于未完整转换的图表或补充材料，暂不强行录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>34</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DOI_10.1126_science.abl4290</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DOI_10.1126_science.abl4290</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Single-nucleus cross-tissue molecular reference maps toward understanding disease gene function.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1126_science.abl4290.md</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>markdown_review_no_formal: Markdown定向复核未发现作者直接给出的正式PNS marker；窗口共现或比较文献基因不录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>35</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DOI_10.1126_science.abo0510</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DOI_10.1126_science.abo0510</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Mapping the developing human immune system across organs.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1126_science.abo0510.md</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>markdown_review_no_formal: Markdown定向复核未发现作者直接给出的正式PNS marker；窗口共现或比较文献基因不录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>39</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DOI_10.1101_2025.09.26.678707</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>DOI_10.1101_2025.09.26.678707</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Cellular and Spatial Drivers of Unresolved Injury and Functional Decline in the Human Kidney</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1101_2025.09.26.678707.md</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>needs_manual_review: Markdown提及PNS细胞，但marker疑位于未完整转换的图表或补充材料，暂不强行录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>40</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41467-021-21783-3</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41467-021-21783-3</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Time-resolved single-cell analysis of Brca1 associated mammary tumourigenesis reveals aberrant differentiation of luminal progenitors.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1038_s41467-021-21783-3.md</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>markdown_review_no_formal: Markdown定向复核未发现作者直接给出的正式PNS marker；窗口共现或比较文献基因不录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>43</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41586-020-2496-1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s41586-020-2496-1</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>A single-cell transcriptomic atlas characterizes ageing tissues in the mouse.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1038_s41586-020-2496-1.md</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>markdown_review_no_formal: Markdown定向复核未发现作者直接给出的正式PNS marker；窗口共现或比较文献基因不录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>B20260814-003</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>44</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s42003-024-07315-x</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>DOI_10.1038_s42003-024-07315-x</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Cross-species single-cell RNA-seq analysis reveals disparate and conserved cardiac and extracardiac inflammatory responses upon heart injury.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>quick_consistency</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>scripts/extract_markers/review_md/DOI_10.1038_s42003-024-07315-x.md</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>markdown_review_no_formal: Markdown定向复核未发现作者直接给出的正式PNS marker；窗口共现或比较文献基因不录入</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
